--- a/Classement_Meuble_TV_LED_AthisMons_2026.xlsx
+++ b/Classement_Meuble_TV_LED_AthisMons_2026.xlsx
@@ -568,7 +568,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rayon : ≤ 25 km Athis-Mons (91200) · Total analysé : 33 annonces · Médiane Marché : 80 € · Mise à jour : 17/09/2026 à 18:55:06</t>
+          <t>Rayon : ≤ 25 km Athis-Mons (91200) · Total analysé : 33 annonces · Médiane Marché : 80 € · Mise à jour : 17/09/2026 à 21:09:56</t>
         </is>
       </c>
     </row>
